--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\chromadb\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F170DA6-C0EC-48E4-B6CA-43EB49E3CD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD7C7BE-FBE5-466B-B6BF-1ADE4CEC79A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>Question</t>
   </si>
@@ -86,6 +86,18 @@
   </si>
   <si>
     <t>no more questions</t>
+  </si>
+  <si>
+    <t>scholarships</t>
+  </si>
+  <si>
+    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship. The HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement. The Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements.</t>
+  </si>
+  <si>
+    <t>dual</t>
+  </si>
+  <si>
+    <t>Dual enrollment allows high school students to take college courses and earn both high school and college credit simultaneously.</t>
   </si>
 </sst>
 </file>
@@ -926,10 +938,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -937,7 +949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -945,7 +957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -953,7 +965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -961,7 +973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -969,7 +981,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -977,7 +989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -985,7 +997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -993,7 +1005,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1001,7 +1013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1009,7 +1021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1017,7 +1029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1025,7 +1037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1033,7 +1045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1041,7 +1053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1049,7 +1061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1057,7 +1069,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1065,7 +1077,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1073,12 +1085,28 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\chromadb\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD7C7BE-FBE5-466B-B6BF-1ADE4CEC79A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75747BB2-6432-4C7D-B823-6F0F880F30AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -1111,5 +1111,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75747BB2-6432-4C7D-B823-6F0F880F30AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72196AF-7362-4746-92B2-7485E3060116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,10 +91,10 @@
     <t>scholarships</t>
   </si>
   <si>
-    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship. The HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement. The Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements.</t>
-  </si>
-  <si>
     <t>dual</t>
+  </si>
+  <si>
+    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.\n\nThe HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.\n\nThe Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
   </si>
   <si>
     <t>Dual enrollment allows high school students to take college courses and earn both high school and college credit simultaneously.</t>
@@ -1098,12 +1098,12 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72196AF-7362-4746-92B2-7485E3060116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C8B610-A82F-435D-9BD9-CD00A0B9C969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
     <t>Hi</t>
   </si>
   <si>
-    <t>Hi, I'm onePal. Happy to help !! You can ask like - scholarships, my academic standing, graduation requirements, etc.</t>
-  </si>
-  <si>
     <t>Good Evening</t>
   </si>
   <si>
@@ -94,10 +91,13 @@
     <t>dual</t>
   </si>
   <si>
-    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.\n\nThe HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.\n\nThe Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
-  </si>
-  <si>
     <t>Dual enrollment allows high school students to take college courses and earn both high school and college credit simultaneously.</t>
+  </si>
+  <si>
+    <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.The HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.The Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
+  </si>
+  <si>
+    <t>Hi, Guidance Genie Here. Happy to help !! You can ask like - scholarships, dual enrollment, my academic standing, graduation requirements, etc.</t>
   </si>
 </sst>
 </file>
@@ -954,148 +954,148 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
         <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
         <v>24</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
         <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C8B610-A82F-435D-9BD9-CD00A0B9C969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67C8BE9-7F67-4BBD-BD7B-34EEBB6738F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67C8BE9-7F67-4BBD-BD7B-34EEBB6738F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320F8C3F-CE05-44F3-989B-0ADC6D41812E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
   <si>
     <t>Question</t>
   </si>
@@ -98,6 +98,12 @@
   </si>
   <si>
     <t>Hi, Guidance Genie Here. Happy to help !! You can ask like - scholarships, dual enrollment, my academic standing, graduation requirements, etc.</t>
+  </si>
+  <si>
+    <t>academic standing</t>
+  </si>
+  <si>
+    <t>What's your Student ID ?</t>
   </si>
 </sst>
 </file>
@@ -938,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1109,6 +1115,14 @@
         <v>23</v>
       </c>
     </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320F8C3F-CE05-44F3-989B-0ADC6D41812E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BAB637-5A6B-41B7-BD15-9F6350116087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="3630" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>Question</t>
   </si>
@@ -104,6 +104,15 @@
   </si>
   <si>
     <t>What's your Student ID ?</t>
+  </si>
+  <si>
+    <t>To graduate, you must complete a certain number of credits in required subjects (e.g., English, math, science, social studies), pass state exams, and fulfill any additional requirements set by your school.</t>
+  </si>
+  <si>
+    <t>graduation</t>
+  </si>
+  <si>
+    <t>graduation requirements</t>
   </si>
 </sst>
 </file>
@@ -944,10 +953,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="43.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultColWidth="43.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -955,7 +964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -963,7 +972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -971,7 +980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -979,7 +988,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -987,7 +996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -995,7 +1004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1003,7 +1012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1011,7 +1020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1019,7 +1028,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1027,7 +1036,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1035,7 +1044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1043,7 +1052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1051,7 +1060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1059,7 +1068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1067,7 +1076,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1075,7 +1084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1083,7 +1092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1091,7 +1100,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1099,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1107,7 +1116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1115,12 +1124,28 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>26</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\PycharmProjects\gatech-practicum\chromadb\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BAB637-5A6B-41B7-BD15-9F6350116087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D281C0B6-BB3C-45A6-8775-DF5411FD995C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="3630" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QnAs" sheetId="1" r:id="rId1"/>
@@ -954,9 +954,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="43.26171875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -964,7 +964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -972,7 +972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -980,7 +980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -988,7 +988,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -996,7 +996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>30</v>
       </c>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D281C0B6-BB3C-45A6-8775-DF5411FD995C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38A7595-EB90-43A0-B393-7234AF6AFD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -596,8 +596,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -953,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1148,6 +1151,9 @@
         <v>28</v>
       </c>
     </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B25" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38A7595-EB90-43A0-B393-7234AF6AFD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D6E826-CC65-47B4-A053-C4BAD3FBB3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
   <si>
     <t>Question</t>
   </si>
@@ -113,6 +113,30 @@
   </si>
   <si>
     <t>graduation requirements</t>
+  </si>
+  <si>
+    <t>Thanks</t>
+  </si>
+  <si>
+    <t>Your are welcome, enjoy the rest of your day !!</t>
+  </si>
+  <si>
+    <t>thank you</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>AP classes are advanced courses that can help you prepare for college-level work. They are often more challenging, but they can improve your college applications and earn you college credit if you score well on the AP exams.</t>
+  </si>
+  <si>
+    <t>advanced courses</t>
+  </si>
+  <si>
+    <t>counselling</t>
+  </si>
+  <si>
+    <t>Sure, what do you want to know. You can ask things like bullying, FAFSA, SAT, ACT, college, etc.</t>
   </si>
 </sst>
 </file>
@@ -596,11 +620,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -956,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="43.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1113,46 +1134,83 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>30</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B26" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B25" s="1"/>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/chromadb/docs/general_qnas.xlsx
+++ b/chromadb/docs/general_qnas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manis\PycharmProjects\gatech-practicum\chromadb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D6E826-CC65-47B4-A053-C4BAD3FBB3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A90AF11-3813-48A9-90FF-7D1E3A770578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,9 +97,6 @@
     <t>We have two major scholarships available - HOPE Scholarship &amp; Zell Miller Scholarship.The HOPE (Helping Outstanding Pupils Educationally) Scholarship is a Georgia state-funded program that provides financial assistance to Georgia residents to attend in-state colleges and universities based on academic achievement.The Zell Miller Scholarship is a more competitive Georgia state-funded scholarship that offers higher financial aid amounts than the HOPE Scholarship and is based on even stricter eligibility requirements. See here for more information - https://www.gafutures.org/hope-state-aid-programs/hope-zell-miller-scholarships/</t>
   </si>
   <si>
-    <t>Hi, Guidance Genie Here. Happy to help !! You can ask like - scholarships, dual enrollment, my academic standing, graduation requirements, etc.</t>
-  </si>
-  <si>
     <t>academic standing</t>
   </si>
   <si>
@@ -137,6 +134,9 @@
   </si>
   <si>
     <t>Sure, what do you want to know. You can ask things like bullying, FAFSA, SAT, ACT, college, etc.</t>
+  </si>
+  <si>
+    <t>Hi, Guidance Genie Here. Happy to help !! You can ask like - scholarships, dual enrollment, my academic standing, graduation requirements, counselling, etc.</t>
   </si>
 </sst>
 </file>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1001,7 +1001,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1009,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1017,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1025,7 +1025,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1033,7 +1033,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1041,7 +1041,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1049,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1057,7 +1057,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1065,7 +1065,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1073,7 +1073,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1081,7 +1081,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1089,7 +1089,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1118,34 +1118,34 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -1166,50 +1166,50 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
         <v>26</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
         <v>34</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
         <v>37</v>
-      </c>
-      <c r="B29" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
